--- a/ultetheto_novenyek.xlsx
+++ b/ultetheto_novenyek.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KapusKevin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KapusKevin\Documents\GitHub\GardenPlanner-March6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6DC931-8BFE-4B98-9F7E-157CFFE1CA56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ABB012-7705-481D-96E5-4E18C29D50CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,12 +220,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -255,11 +261,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -638,80 +645,80 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
     </row>

--- a/ultetheto_novenyek.xlsx
+++ b/ultetheto_novenyek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KapusKevin\Documents\GitHub\GardenPlanner-March6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ABB012-7705-481D-96E5-4E18C29D50CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE2A0FD-A8BF-46DA-95E1-2405233D8099}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -723,28 +723,28 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/ultetheto_novenyek.xlsx
+++ b/ultetheto_novenyek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KapusKevin\Documents\GitHub\GardenPlanner-March6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admill\Documents\GitHub\GardenPlanner-March6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE2A0FD-A8BF-46DA-95E1-2405233D8099}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F84C009-261C-4AE5-A300-8CD76ED8BAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,6 +230,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,12 +267,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -285,9 +292,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -325,9 +332,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -360,26 +367,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -412,26 +402,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -606,19 +579,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="67.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -644,7 +617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -663,14 +636,14 @@
       <c r="F2" s="2">
         <v>40</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -689,14 +662,14 @@
       <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -715,14 +688,14 @@
       <c r="F4" s="2">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -741,14 +714,14 @@
       <c r="F5" s="2">
         <v>30</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -774,7 +747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -800,7 +773,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -826,7 +799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -852,7 +825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -878,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>

--- a/ultetheto_novenyek.xlsx
+++ b/ultetheto_novenyek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admill\Documents\GitHub\GardenPlanner-March6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F84C009-261C-4AE5-A300-8CD76ED8BAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C54F4D-A518-4BF1-BCEA-97FA8C37EEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ultetheto_novenyek.xlsx
+++ b/ultetheto_novenyek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admill\Documents\GitHub\GardenPlanner-March6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C54F4D-A518-4BF1-BCEA-97FA8C37EEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A47D21A-24EA-4368-99F7-46E02CC253A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="156" yWindow="228" windowWidth="22884" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,12 +230,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,13 +261,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -636,7 +629,7 @@
       <c r="F2" s="2">
         <v>40</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -662,7 +655,7 @@
       <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -688,7 +681,7 @@
       <c r="F4" s="2">
         <v>20</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -714,7 +707,7 @@
       <c r="F5" s="2">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -722,54 +715,54 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>25</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>75</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>58</v>
       </c>
     </row>
